--- a/file/table/IDER.xlsx
+++ b/file/table/IDER.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Descargas\IDER\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.GISMobile\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8C42068-9397-4778-9D12-99E713D8D5E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD968035-B49F-4F73-A288-C0346271E780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{FD244727-BA1D-4C18-8701-74B68BFFAF93}"/>
+    <workbookView xWindow="-28898" yWindow="6368" windowWidth="28996" windowHeight="15675" xr2:uid="{FD244727-BA1D-4C18-8701-74B68BFFAF93}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1250,6 +1250,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC94A58F-42F1-43DA-9A5F-FC1FCA0219C7}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:E117"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1278,7 +1279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
         <v>25001</v>
       </c>
@@ -1288,7 +1289,7 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>25019</v>
       </c>
@@ -1305,7 +1306,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>25035</v>
       </c>
@@ -1322,7 +1323,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>25040</v>
       </c>
@@ -1339,7 +1340,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>25053</v>
       </c>
@@ -1356,7 +1357,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>25086</v>
       </c>
@@ -1364,7 +1365,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>25095</v>
       </c>
@@ -1381,7 +1382,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>25099</v>
       </c>
@@ -1389,7 +1390,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>25120</v>
       </c>
@@ -1397,7 +1398,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
         <v>25123</v>
       </c>
@@ -1414,7 +1415,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A12" s="1">
         <v>25126</v>
       </c>
@@ -1422,7 +1423,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A13" s="1">
         <v>25148</v>
       </c>
@@ -1430,7 +1431,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
         <v>25151</v>
       </c>
@@ -1438,7 +1439,7 @@
         <v>35</v>
       </c>
       <c r="C14" s="4">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>142</v>
@@ -1447,7 +1448,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A15" s="1">
         <v>25154</v>
       </c>
@@ -1455,7 +1456,7 @@
         <v>36</v>
       </c>
       <c r="C15" s="4">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>144</v>
@@ -1464,7 +1465,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
         <v>25168</v>
       </c>
@@ -1478,7 +1479,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A17" s="1">
         <v>25175</v>
       </c>
@@ -1486,7 +1487,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A18" s="1">
         <v>25178</v>
       </c>
@@ -1494,7 +1495,7 @@
         <v>39</v>
       </c>
       <c r="C18" s="4">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>149</v>
@@ -1503,7 +1504,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A19" s="1">
         <v>25181</v>
       </c>
@@ -1511,7 +1512,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A20" s="1">
         <v>25183</v>
       </c>
@@ -1519,7 +1520,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A21" s="1">
         <v>25200</v>
       </c>
@@ -1536,7 +1537,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A22" s="1">
         <v>25214</v>
       </c>
@@ -1544,7 +1545,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A23" s="1">
         <v>25224</v>
       </c>
@@ -1558,7 +1559,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A24" s="1">
         <v>25245</v>
       </c>
@@ -1575,7 +1576,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A25" s="1">
         <v>25258</v>
       </c>
@@ -1592,7 +1593,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A26" s="1">
         <v>25260</v>
       </c>
@@ -1609,7 +1610,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A27" s="1">
         <v>25269</v>
       </c>
@@ -1626,7 +1627,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A28" s="1">
         <v>25279</v>
       </c>
@@ -1634,7 +1635,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A29" s="1">
         <v>25281</v>
       </c>
@@ -1651,7 +1652,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A30" s="1">
         <v>25286</v>
       </c>
@@ -1659,7 +1660,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A31" s="1">
         <v>25288</v>
       </c>
@@ -1676,7 +1677,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A32" s="1">
         <v>25290</v>
       </c>
@@ -1690,7 +1691,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A33" s="1">
         <v>25293</v>
       </c>
@@ -1707,7 +1708,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A34" s="1">
         <v>25295</v>
       </c>
@@ -1715,7 +1716,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A35" s="1">
         <v>25297</v>
       </c>
@@ -1729,7 +1730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A36" s="1">
         <v>25299</v>
       </c>
@@ -1746,7 +1747,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A37" s="1">
         <v>25307</v>
       </c>
@@ -1754,7 +1755,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A38" s="1">
         <v>25312</v>
       </c>
@@ -1771,7 +1772,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A39" s="1">
         <v>25317</v>
       </c>
@@ -1788,7 +1789,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A40" s="1">
         <v>25320</v>
       </c>
@@ -1805,7 +1806,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A41" s="1">
         <v>25322</v>
       </c>
@@ -1813,7 +1814,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A42" s="1">
         <v>25324</v>
       </c>
@@ -1821,7 +1822,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A43" s="1">
         <v>25326</v>
       </c>
@@ -1838,7 +1839,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A44" s="1">
         <v>25328</v>
       </c>
@@ -1855,7 +1856,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A45" s="1">
         <v>25335</v>
       </c>
@@ -1872,7 +1873,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A46" s="1">
         <v>25339</v>
       </c>
@@ -1880,7 +1881,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A47" s="1">
         <v>25368</v>
       </c>
@@ -1897,7 +1898,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A48" s="1">
         <v>25372</v>
       </c>
@@ -1914,7 +1915,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A49" s="1">
         <v>25377</v>
       </c>
@@ -1922,7 +1923,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A50" s="1">
         <v>25386</v>
       </c>
@@ -1939,7 +1940,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A51" s="1">
         <v>25394</v>
       </c>
@@ -1956,7 +1957,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A52" s="1">
         <v>25398</v>
       </c>
@@ -1964,7 +1965,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A53" s="1">
         <v>25402</v>
       </c>
@@ -1972,7 +1973,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A54" s="1">
         <v>25407</v>
       </c>
@@ -1989,7 +1990,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A55" s="1">
         <v>25426</v>
       </c>
@@ -1997,7 +1998,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A56" s="1">
         <v>25430</v>
       </c>
@@ -2005,7 +2006,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A57" s="1">
         <v>25436</v>
       </c>
@@ -2022,7 +2023,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A58" s="1">
         <v>25438</v>
       </c>
@@ -2039,7 +2040,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A59" s="1">
         <v>25473</v>
       </c>
@@ -2047,7 +2048,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A60" s="1">
         <v>25483</v>
       </c>
@@ -2064,7 +2065,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A61" s="1">
         <v>25486</v>
       </c>
@@ -2081,7 +2082,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A62" s="1">
         <v>25488</v>
       </c>
@@ -2089,7 +2090,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A63" s="1">
         <v>25489</v>
       </c>
@@ -2106,7 +2107,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A64" s="1">
         <v>25491</v>
       </c>
@@ -2123,7 +2124,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A65" s="1">
         <v>25506</v>
       </c>
@@ -2140,7 +2141,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A66" s="1">
         <v>25513</v>
       </c>
@@ -2148,7 +2149,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A67" s="1">
         <v>25518</v>
       </c>
@@ -2165,7 +2166,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A68" s="1">
         <v>25524</v>
       </c>
@@ -2182,7 +2183,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A69" s="1">
         <v>25530</v>
       </c>
@@ -2199,7 +2200,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A70" s="1">
         <v>25535</v>
       </c>
@@ -2216,7 +2217,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A71" s="1">
         <v>25572</v>
       </c>
@@ -2224,7 +2225,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A72" s="1">
         <v>25580</v>
       </c>
@@ -2241,7 +2242,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A73" s="1">
         <v>25592</v>
       </c>
@@ -2258,7 +2259,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A74" s="1">
         <v>25594</v>
       </c>
@@ -2275,7 +2276,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A75" s="1">
         <v>25596</v>
       </c>
@@ -2292,7 +2293,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A76" s="1">
         <v>25599</v>
       </c>
@@ -2309,7 +2310,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A77" s="1">
         <v>25612</v>
       </c>
@@ -2317,7 +2318,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A78" s="1">
         <v>25645</v>
       </c>
@@ -2334,7 +2335,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A79" s="1">
         <v>25649</v>
       </c>
@@ -2342,7 +2343,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A80" s="1">
         <v>25653</v>
       </c>
@@ -2359,7 +2360,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A81" s="1">
         <v>25658</v>
       </c>
@@ -2367,7 +2368,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A82" s="1">
         <v>25662</v>
       </c>
@@ -2384,7 +2385,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A83" s="1">
         <v>25718</v>
       </c>
@@ -2401,7 +2402,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A84" s="1">
         <v>25736</v>
       </c>
@@ -2409,7 +2410,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A85" s="1">
         <v>25740</v>
       </c>
@@ -2417,7 +2418,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A86" s="1">
         <v>25743</v>
       </c>
@@ -2434,7 +2435,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A87" s="1">
         <v>25745</v>
       </c>
@@ -2450,13 +2451,13 @@
         <v>102</v>
       </c>
       <c r="C88" s="4">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A89" s="1">
         <v>25758</v>
       </c>
@@ -2464,7 +2465,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A90" s="1">
         <v>25769</v>
       </c>
@@ -2481,7 +2482,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A91" s="1">
         <v>25772</v>
       </c>
@@ -2489,7 +2490,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A92" s="1">
         <v>25777</v>
       </c>
@@ -2506,7 +2507,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A93" s="1">
         <v>25779</v>
       </c>
@@ -2523,7 +2524,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A94" s="1">
         <v>25781</v>
       </c>
@@ -2540,7 +2541,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A95" s="1">
         <v>25785</v>
       </c>
@@ -2548,7 +2549,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A96" s="1">
         <v>25793</v>
       </c>
@@ -2565,7 +2566,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A97" s="1">
         <v>25797</v>
       </c>
@@ -2582,7 +2583,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A98" s="1">
         <v>25799</v>
       </c>
@@ -2590,7 +2591,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A99" s="1">
         <v>25805</v>
       </c>
@@ -2607,7 +2608,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A100" s="1">
         <v>25807</v>
       </c>
@@ -2624,7 +2625,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A101" s="1">
         <v>25815</v>
       </c>
@@ -2641,7 +2642,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A102" s="1">
         <v>25817</v>
       </c>
@@ -2649,7 +2650,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A103" s="1">
         <v>25823</v>
       </c>
@@ -2657,7 +2658,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A104" s="1">
         <v>25839</v>
       </c>
@@ -2674,7 +2675,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A105" s="1">
         <v>25841</v>
       </c>
@@ -2691,7 +2692,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A106" s="1">
         <v>25843</v>
       </c>
@@ -2708,7 +2709,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A107" s="1">
         <v>25845</v>
       </c>
@@ -2725,7 +2726,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A108" s="1">
         <v>25851</v>
       </c>
@@ -2733,7 +2734,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A109" s="1">
         <v>25862</v>
       </c>
@@ -2750,7 +2751,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A110" s="1">
         <v>25867</v>
       </c>
@@ -2767,7 +2768,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A111" s="1">
         <v>25871</v>
       </c>
@@ -2784,7 +2785,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A112" s="1">
         <v>25873</v>
       </c>
@@ -2801,7 +2802,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A113" s="1">
         <v>25875</v>
       </c>
@@ -2818,7 +2819,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A114" s="1">
         <v>25878</v>
       </c>
@@ -2835,7 +2836,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A115" s="1">
         <v>25885</v>
       </c>
@@ -2849,7 +2850,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A116" s="1">
         <v>25898</v>
       </c>
@@ -2881,7 +2882,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E117" xr:uid="{AC94A58F-42F1-43DA-9A5F-FC1FCA0219C7}"/>
+  <autoFilter ref="A1:E117" xr:uid="{AC94A58F-42F1-43DA-9A5F-FC1FCA0219C7}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="2022"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E117">
     <sortCondition ref="A2:A117"/>
   </sortState>
